--- a/Side Bar Files/GWD Data/ZCost Index.xlsx
+++ b/Side Bar Files/GWD Data/ZCost Index.xlsx
@@ -269,7 +269,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_12" displayName="Table_12" ref="A1:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_14" displayName="Table_14" ref="A1:B16">
   <tableColumns count="2">
     <tableColumn id="1" name="District"/>
     <tableColumn id="2" name="Index"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B0B40C0-5BF3-4EDC-A852-7F0224FCB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C28DC61-BDD5-45C1-889B-7B49BFCDB9A7}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/ZCost Index.xlsx
+++ b/Side Bar Files/GWD Data/ZCost Index.xlsx
@@ -117,25 +117,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -150,11 +136,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -269,7 +255,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_14" displayName="Table_14" ref="A1:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_15" displayName="Table_15" ref="A1:B16">
   <tableColumns count="2">
     <tableColumn id="1" name="District"/>
     <tableColumn id="2" name="Index"/>
@@ -574,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C28DC61-BDD5-45C1-889B-7B49BFCDB9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7736C567-502D-44BA-95BA-5EDE5DA6BAA6}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/ZCost Index.xlsx
+++ b/Side Bar Files/GWD Data/ZCost Index.xlsx
@@ -560,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7736C567-502D-44BA-95BA-5EDE5DA6BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3FAF85A-0778-4725-A723-A23F2A8DBAA6}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/ZCost Index.xlsx
+++ b/Side Bar Files/GWD Data/ZCost Index.xlsx
@@ -169,7 +169,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="ZCost Index-style" pivot="0" table="0" count="3">
+    <tableStyle name="zCost Index-style" pivot="0" table="0" count="3">
       <tableStyleElement type="headerRow" dxfId="0"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="2"/>
@@ -255,12 +255,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_15" displayName="Table_15" ref="A1:B16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_13" displayName="Table_13" ref="A1:B16">
   <tableColumns count="2">
     <tableColumn id="1" name="District"/>
     <tableColumn id="2" name="Index"/>
   </tableColumns>
-  <tableStyleInfo name="ZCost Index-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="zCost Index-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -560,7 +560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3FAF85A-0778-4725-A723-A23F2A8DBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F83EE55-3055-4314-8988-A8C3B689BAA6}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
